--- a/Rekap_Transaksi_Dengan_Gambar.xlsx
+++ b/Rekap_Transaksi_Dengan_Gambar.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +53,17 @@
       <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -80,7 +91,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -116,11 +127,55 @@
         <color rgb="001E293B"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001E293B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001E293B"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -158,6 +213,19 @@
     <xf numFmtId="3" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -257,6 +325,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -282,6 +353,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -307,6 +381,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -332,6 +409,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -357,6 +437,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -382,6 +465,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -407,6 +493,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -432,6 +521,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -457,6 +549,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -482,6 +577,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -507,6 +605,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -532,6 +633,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -557,6 +661,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -582,6 +689,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -607,6 +717,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -632,6 +745,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -657,6 +773,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -682,6 +801,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -707,6 +829,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -732,6 +857,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -757,6 +885,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -782,6 +913,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -807,6 +941,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -832,6 +969,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -857,6 +997,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -882,6 +1025,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -907,6 +1053,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -932,6 +1081,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -957,6 +1109,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -982,6 +1137,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1007,6 +1165,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1032,6 +1193,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1051,6 +1215,84 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="466725" cy="1190625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="466725" cy="1190625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="466725" cy="1190625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1353,7 +1595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2544,26 +2786,123 @@
       </c>
       <c r="H37" s="7" t="n"/>
     </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+    <row r="38" ht="100" customHeight="1">
+      <c r="A38" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02 09:48:07</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>BCA (697-5**-**89)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Transfer BCA VA</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>DANA - DNID SUYXXXX (3901089524731672)</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-14 at 20.13.00 (1).jpeg</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H38" s="16" t="n"/>
+    </row>
+    <row r="39" ht="100" customHeight="1">
+      <c r="A39" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:14:20</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>BCA (697-5**-**89)</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Transfer BCA VA</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>DANA - DNID SUYXXXX (3901089524731672)</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-14 at 20.13.00.jpeg</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H39" s="16" t="n"/>
+    </row>
+    <row r="40" ht="100" customHeight="1">
+      <c r="A40" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:22:11</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>BCA (697-5**-**89)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Transfer BCA VA</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>DANA - DNID SUYXXXX (3901089524731672)</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>WhatsApp Image 2026-10-14 at 20.12.59.jpeg</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>550000</v>
+      </c>
+      <c r="H40" s="16" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>TOTAL KESELURUHAN</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14">
-        <f>SUM(G5:G37)</f>
+      <c r="G41" s="18">
+        <f>SUM(G5:G40)</f>
         <v/>
       </c>
-      <c r="H38" s="13" t="n"/>
+      <c r="H41" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
